--- a/每日输出/石家庄初短/石家庄-石家庄初短-每日风灵不在线.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-每日风灵不在线.xlsx
@@ -7022,7 +7022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -7148,17 +7148,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -7167,16 +7167,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -7186,12 +7181,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -7211,7 +7206,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7226,7 +7221,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7236,17 +7231,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -7259,7 +7254,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -7269,12 +7264,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -7294,7 +7289,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7309,7 +7304,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7319,17 +7314,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -7338,11 +7333,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -7352,12 +7352,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7402,17 +7402,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7421,16 +7421,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -7440,12 +7435,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -7465,7 +7460,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7480,7 +7475,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7490,17 +7485,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7509,11 +7504,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7573,17 +7573,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7661,17 +7661,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7851,11 +7851,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -7865,12 +7870,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -7890,7 +7895,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7905,7 +7910,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7915,17 +7920,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7943,7 +7948,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -7953,12 +7958,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -7978,7 +7983,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8003,17 +8008,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -8022,12 +8027,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8091,17 +8091,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -8286,12 +8286,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -8305,12 +8300,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -8330,7 +8325,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8345,7 +8340,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8355,17 +8350,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -8374,16 +8369,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -8393,12 +8383,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -8418,7 +8408,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8448,12 +8438,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8476,12 +8466,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -8501,7 +8491,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8516,7 +8506,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8526,17 +8516,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8545,16 +8535,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -8564,12 +8549,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -8589,7 +8574,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8604,7 +8589,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -8614,17 +8599,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8642,7 +8627,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -8652,12 +8637,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -8677,7 +8662,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8692,7 +8677,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -8702,17 +8687,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8721,16 +8706,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -8740,12 +8720,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -8765,7 +8745,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8795,12 +8775,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -8828,12 +8808,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -8853,7 +8833,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8883,12 +8863,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -8911,12 +8891,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -8936,7 +8916,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8951,7 +8931,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8961,17 +8941,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8980,11 +8960,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -8994,12 +8979,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -9019,7 +9004,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9034,7 +9019,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -9044,17 +9029,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -9063,16 +9048,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -9082,12 +9062,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -9107,7 +9087,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9122,7 +9102,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -9132,17 +9112,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -9151,16 +9131,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -9170,12 +9145,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -9195,7 +9170,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9225,12 +9200,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -9239,7 +9214,12 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -9253,12 +9233,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -9278,7 +9258,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9293,7 +9273,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9303,17 +9283,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -9322,16 +9302,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -9341,12 +9316,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -9366,7 +9341,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9381,7 +9356,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9391,17 +9366,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -9410,16 +9385,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6,7,8,9,17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -9429,12 +9404,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -9454,7 +9429,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9469,7 +9444,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9479,17 +9454,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -9498,11 +9473,16 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -9512,12 +9492,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -9537,7 +9517,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9567,12 +9547,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9595,12 +9575,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -9620,7 +9600,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9635,7 +9615,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9645,17 +9625,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9664,16 +9644,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -9683,12 +9658,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -9708,7 +9683,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9723,7 +9698,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9733,17 +9708,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9752,11 +9727,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>9,10</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -9766,12 +9746,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -9791,7 +9771,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9821,12 +9801,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -9835,12 +9815,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9854,12 +9829,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -9879,7 +9854,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9904,17 +9879,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -9942,12 +9917,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -9967,7 +9942,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9982,7 +9957,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9992,17 +9967,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -10011,11 +9986,16 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -10025,12 +10005,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -10050,7 +10030,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10065,7 +10045,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10075,17 +10055,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -10094,16 +10074,16 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -10113,12 +10093,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -10138,7 +10118,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10168,12 +10148,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -10182,7 +10162,12 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10196,12 +10181,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -10221,7 +10206,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10236,7 +10221,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -10246,17 +10231,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -10265,16 +10250,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -10284,12 +10264,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -10309,7 +10289,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10324,7 +10304,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10334,17 +10314,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -10353,16 +10333,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -10372,12 +10347,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -10397,7 +10372,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10412,7 +10387,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -10422,17 +10397,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -10441,16 +10416,16 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -10460,12 +10435,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -10485,7 +10460,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -10510,17 +10485,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -10529,11 +10504,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -10548,12 +10523,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -10573,7 +10548,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10588,7 +10563,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -10598,17 +10573,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -10617,16 +10592,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -10636,12 +10606,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -10661,7 +10631,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10676,7 +10646,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -10686,17 +10656,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -10705,11 +10675,16 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -10719,12 +10694,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -10744,7 +10719,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10759,7 +10734,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -10769,17 +10744,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -10797,7 +10772,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -10807,12 +10782,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -10832,7 +10807,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10847,7 +10822,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -10857,17 +10832,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -10876,11 +10851,16 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -10890,12 +10870,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -10915,7 +10895,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10930,7 +10910,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -10940,17 +10920,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -10968,7 +10948,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -10978,12 +10958,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -11003,7 +10983,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -11028,17 +11008,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -11061,12 +11041,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -11086,7 +11066,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -11101,7 +11081,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11111,17 +11091,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -11130,16 +11110,16 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -11149,12 +11129,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -11174,7 +11154,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -11189,7 +11169,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -11199,17 +11179,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -11227,7 +11207,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -11237,12 +11217,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -11262,7 +11242,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11277,7 +11257,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -11287,17 +11267,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -11306,16 +11286,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -11325,12 +11305,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -11350,7 +11330,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11375,17 +11355,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -11394,11 +11374,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -11413,12 +11393,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -11438,7 +11418,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11453,7 +11433,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11463,17 +11443,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -11482,16 +11462,16 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -11501,12 +11481,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -11526,7 +11506,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11541,7 +11521,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -11551,17 +11531,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -11570,11 +11550,16 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -11584,12 +11569,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -11609,7 +11594,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11624,7 +11609,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -11634,17 +11619,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -11653,16 +11638,11 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -11672,12 +11652,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -11697,7 +11677,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -11712,7 +11692,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11722,17 +11702,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -11750,7 +11730,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -11760,12 +11740,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -11785,7 +11765,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11800,7 +11780,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11810,17 +11790,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -11829,11 +11809,16 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -11843,12 +11828,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -11868,7 +11853,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11883,7 +11868,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11893,17 +11878,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -11912,16 +11897,11 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -11931,12 +11911,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -11956,7 +11936,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11971,7 +11951,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11981,17 +11961,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -12000,16 +11980,16 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -12019,12 +11999,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -12044,7 +12024,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12059,7 +12039,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12069,17 +12049,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -12088,11 +12068,16 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -12102,12 +12087,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -12127,7 +12112,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12157,12 +12142,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -12171,7 +12156,12 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -12185,12 +12175,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -12210,7 +12200,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12225,7 +12215,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12235,17 +12225,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -12254,11 +12244,16 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -12268,12 +12263,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -12293,7 +12288,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12308,7 +12303,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12318,17 +12313,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -12346,7 +12341,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -12356,12 +12351,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -12381,7 +12376,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12396,7 +12391,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12406,17 +12401,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -12434,7 +12429,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -12444,12 +12439,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -12469,7 +12464,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12484,63 +12479,1192 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>zhangxuqing</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>张旭青</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>zhangxuqing</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>张旭青</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>liyixin</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>李奕昕</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>liyixin</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>李奕昕</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>lvzhenyang</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>吕禛杨</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>lvzhenyang</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>吕禛杨</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>fengyifan01</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>22,23</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>fengyifan01</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>石家庄</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>新兵营-出</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>zhangjing03</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>张菁</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>zhangjing03</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>张菁</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>liuxiaosong</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>liuxiaosong</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>yangpengfei</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>杨鹏飞</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>yangpengfei</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>杨鹏飞</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>caotianao</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>曹添傲</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>caotianao</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>曹添傲</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>长期班</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>曹晓雨</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>caoxiaoyu</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>曹晓雨</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="K73" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>caoxiaoyu</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>曹晓雨</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>weixiaodi</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>卫晓迪</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>weixiaodi</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>卫晓迪</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>caoxiaoyu</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>曹晓雨</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>limengyao03</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>李梦瑶</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>limengyao03</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>李梦瑶</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -12557,7 +13681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12702,8 +13826,8 @@
       <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>0.2777777777777778</v>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12826,8 +13950,8 @@
       <c r="F9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>0.6666666666666666</v>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -12858,7 +13982,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="11">
@@ -13260,8 +14384,8 @@
       <c r="F23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="5" t="n">
-        <v>0.4444444444444444</v>
+      <c r="G23" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13322,8 +14446,8 @@
       <c r="F25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>0.6111111111111112</v>
+      <c r="G25" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -13385,7 +14509,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="28">
@@ -13561,17 +14685,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>张亦浩</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.6666666666666666</v>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="34">
@@ -13592,11 +14716,11 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>1</v>
@@ -13623,11 +14747,11 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>1</v>
+          <t>张子璇</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.5555555555555556</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>1</v>
@@ -13654,7 +14778,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
@@ -13685,17 +14809,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>陈利辉</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.9444444444444444</v>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -13716,17 +14840,17 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>黄诺</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>1</v>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.9444444444444444</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>0</v>
+      <c r="G38" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -13737,21 +14861,21 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>张迎</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
+          <t>黄诺</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>1</v>
@@ -13778,17 +14902,17 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>1</v>
+          <t>张迎</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="41">
@@ -13809,17 +14933,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>曹添傲</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
+          <t>曹晓雨</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G41" s="3" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="42">
@@ -13840,11 +14964,11 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>1</v>
@@ -13871,17 +14995,17 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="F43" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="F43" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G43" s="5" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -13902,16 +15026,47 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
           <t>王星晨</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="n">
+      <c r="E45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-每日风灵不在线.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-每日风灵不在线.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,66 +620,64 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1688858289869798</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1688854894759300</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>吕禛杨</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>lvzhenyang</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>冯一帆</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fengyifan01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -719,37 +717,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1688857703847806</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1688854281870569</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -773,17 +769,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -823,37 +819,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1688854776688740</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1688858289869798</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -865,11 +859,11 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>22,23</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -877,17 +871,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -927,37 +921,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1688854470818602</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1688854603884803</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -976,17 +968,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1016,7 +1008,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>短期班</t>
+          <t>长期班</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1026,37 +1018,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1688858199721276</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1688855600786055</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1065,27 +1055,42 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1125,37 +1130,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1688858124858856</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1688854776688740</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1164,42 +1167,27 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1239,66 +1227,64 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1688855928851644</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1688857751871196</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>杨佳雪</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>yangjiaxue</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>杨璐</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>yanglu</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1338,37 +1324,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1688856312814793</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1688854894759481</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1377,27 +1361,42 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1437,37 +1436,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1688854894759300</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1688854281870561</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1479,24 +1476,29 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1536,37 +1538,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1688858008853709</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1688857392814199</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1581,26 +1581,21 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1640,71 +1635,64 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1688854287853916</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1688856624782683</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>张硕辉</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>zhangshuohui01</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>谷豪华</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>guhaohua</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1744,37 +1732,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1688854522754361</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1688857703847806</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1786,24 +1772,29 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1843,37 +1834,35 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1688854894759430</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1688856819940740</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1892,17 +1881,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1942,37 +1931,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1688857372708211</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1688855270890491</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1984,24 +1971,29 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2041,37 +2033,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1688854281870561</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1688857790837398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2080,32 +2070,42 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,20,21,22,23</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2145,37 +2145,35 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1688854706800124</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1688856261784494</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2187,24 +2185,29 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2244,66 +2247,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1688855770825630</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1688856920865401</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>liuxiaosong</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>高佳华</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>gaojiahua</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2343,37 +2349,35 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1688855270890470</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1688854497763413</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2385,29 +2389,24 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2447,37 +2446,35 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1688854476856492</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1688854815837469</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2489,29 +2486,24 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2551,37 +2543,35 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1688855593838985</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1688855686929440</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2593,11 +2583,11 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2605,17 +2595,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2655,66 +2645,64 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1688854894759558</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1688855581862225</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>张子璇</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>zhangzixuan03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>胡茹茹</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>hururu</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2754,37 +2742,35 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1688858124858984</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1688857145762192</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2796,29 +2782,24 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2858,71 +2839,64 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1688854281870550</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1688854476856420</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>李雨薇</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>liyuwei</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>初一</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>王紫东</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>wangzidong</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>6,7,8,9,17,18</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2962,37 +2936,35 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1688855270890491</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1688854575781532</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3004,29 +2976,29 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3066,37 +3038,35 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1688856644818249</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1688854522754461</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3108,24 +3078,29 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3165,37 +3140,35 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1688855070755789</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1688854281870530</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3207,24 +3180,29 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3264,71 +3242,64 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1688855581862225</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1688855928851644</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>杨璐</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>yanglu</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>张子璇</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>zhangzixuan03</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>9,10,11,12,13,14,15,16</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3368,37 +3339,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1688854815837469</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1688858124858984</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3410,24 +3379,29 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10,11</t>
+        </is>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3467,37 +3441,35 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1688857145762192</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1688854784881054</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3509,24 +3481,29 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3566,13 +3543,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1688854575781532</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1688854784881058</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3586,17 +3561,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3608,7 +3583,12 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -3620,12 +3600,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3665,37 +3645,35 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1688855477810382</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1688857605746717</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3714,17 +3692,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3764,66 +3742,64 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1688857691776053</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1688856312814793</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>张瑶森</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>zhangyaosen</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>张亮亮</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>zhangliangliang</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3863,66 +3839,64 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1688854522753923</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1688854476856492</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>张一卓</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>zhangyizhuo01</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>刘莹凤</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>liuyingfeng</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3962,71 +3936,64 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1688854287853891</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1688855770825630</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>高佳华</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>gaojiahua</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>niuwei</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4066,37 +4033,35 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1688854497763413</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1688857372708211</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4115,17 +4080,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4165,37 +4130,35 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1688858124858906</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1688855270890436</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4219,17 +4182,17 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4269,66 +4232,64 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1688857392814199</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1688855086834341</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>魏晨阳</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>weichenyang</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>申谭谭</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>shentantan</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4368,37 +4329,35 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1688855600786055</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1688855270890470</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4410,29 +4369,29 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4472,37 +4431,35 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1688856920865401</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1688854281870550</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4514,11 +4471,11 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,19,20,21</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -4526,17 +4483,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4576,37 +4533,35 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1688855086834341</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1688855270890446</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4618,24 +4573,29 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4675,66 +4635,64 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1688857254754511</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1688854894759558</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>胡茹茹</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>hururu</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>李旭东</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>lixudong</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4774,71 +4732,64 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1688855270890436</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1688855477810382</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>李奕昕</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>liyixin</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
           <t>初一</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>张学伦</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>zhangxuelun01</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4878,37 +4829,35 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1688854522754461</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1688857254754511</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4920,29 +4869,24 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4982,71 +4926,64 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1688854761929635</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1688854497763364</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>yangbolan</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>张亦浩</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>zhangyihao</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5086,13 +5023,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1688857455845397</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1688854784881061</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5106,17 +5041,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5145,12 +5080,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5190,37 +5125,35 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1688854603884803</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1688854706800124</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5232,29 +5165,24 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5294,13 +5222,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1688856819940740</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1688854784881036</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5314,17 +5240,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5336,7 +5262,12 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -5348,12 +5279,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5393,37 +5324,35 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1688854497763364</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1688855593838985</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5435,24 +5364,29 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5492,71 +5426,69 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1688855564781214</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1688854761929635</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>张亦浩</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>zhangyihao</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>10,11,12,13,14,15,16,17</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>陈利辉</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>chenlihui</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5596,66 +5528,64 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1688855473818358</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1688854260743321</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>杨鹏飞</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>yangpengfei</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>吴相宏</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>wuxianghong02</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5695,71 +5625,64 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1688855270890446</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1688854470818602</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>孙宇哲</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>sunyuzhe</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>谷晨旭</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>guchenxu</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5799,37 +5722,35 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1688854281870569</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1688857691776053</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5841,29 +5762,24 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5903,37 +5819,35 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1688855292870141</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1688856261784534</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5945,11 +5859,11 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>14,15,16,17,18,19,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -5957,17 +5871,17 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6007,37 +5921,35 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1688857605746717</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1688854287853916</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6046,27 +5958,42 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6106,37 +6033,35 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1688854260743321</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1688856644818249</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6148,29 +6073,24 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6210,66 +6130,64 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1688857751871196</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1688855070755789</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>严绍源</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>yanshaoyuan</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>杨佳雪</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>yangjiaxue</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6309,66 +6227,64 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1688854572834470</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1688855473818358</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>吴相宏</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>wuxianghong02</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>张浩</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>zhanghao06</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6408,37 +6324,35 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1688855827846478</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1688854522754143</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6447,42 +6361,27 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6522,13 +6421,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1688854706799328</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1688857790837033</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6542,17 +6439,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6564,7 +6461,12 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -6576,12 +6478,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6621,37 +6523,35 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1688854281870530</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1688858199721276</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6663,29 +6563,24 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6725,37 +6620,35 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1688854522754143</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1688854706799328</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6774,17 +6667,17 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6824,37 +6717,35 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1688854476856420</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1688857790837332</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6866,11 +6757,11 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,20,21,22,23</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -6878,17 +6769,17 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6928,84 +6819,1393 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1688856624782683</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1688855564781214</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>chenlihui</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>chenlihui</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1688855292870141</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>赵世文</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>zhaoshiwen</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>赵世文</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>zhaoshiwen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1688854894759430</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>黄诺</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>huangnuo</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>黄诺</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>huangnuo</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1688858008853709</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>耿亚轩</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>gengyaxuan</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>耿亚轩</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>gengyaxuan</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1688854784881034</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>renchaoyue</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>renchaoyue</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1688855827846478</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>wangxuyang01</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,22,23</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>wangxuyang01</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1688854572834470</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>zhanghao06</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>zhanghao06</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1688854522754361</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1688854522753923</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>刘莹凤</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>liuyingfeng</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>刘莹凤</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>liuyingfeng</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1688858124858856</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>王佳琦</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>wangjiaqi05</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>王佳琦</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>wangjiaqi05</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1688854287853891</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>niuwei</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>niuwei</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1688858124858906</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>天天向上</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>张硕辉</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>zhangshuohui01</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>刘晓娜</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>liuxiaona</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="M64" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="inlineStr">
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="inlineStr">
         <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>张硕辉</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>zhangshuohui01</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>刘晓娜</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>liuxiaona</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1688857455845397</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>张迎</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>zhangying04</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>9,10,11,12,13,14,15,16,22</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>张迎</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>zhangying04</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1688854784881059</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>仲欣琦</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>zhongxinqi</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>仲欣琦</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>zhongxinqi</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -13681,7 +14881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13696,7 +14896,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>风灵在线未达标名单（石家庄初短）-9月14日（低价课）</t>
+          <t>风灵在线未达标名单（石家庄初短）-9月16日（低价课）</t>
         </is>
       </c>
     </row>
@@ -13750,22 +14950,22 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.4444444444444444</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="4">
@@ -13786,11 +14986,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -13817,17 +15017,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13941,17 +15141,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
+      <c r="G9" s="5" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="10">
@@ -13972,17 +15172,17 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -14003,17 +15203,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14034,7 +15234,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -14055,21 +15255,21 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>郭少华</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
+          <t>刘晓娜</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>1</v>
@@ -14086,24 +15286,24 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>1</v>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.9444444444444444</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
@@ -14127,11 +15327,11 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
+          <t>姜傲爽</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>1</v>
@@ -14158,11 +15358,11 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>刘晓松</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.5</v>
+          <t>张硕辉</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>1</v>
@@ -14189,14 +15389,14 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>1</v>
+          <t>谷豪华</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
@@ -14220,11 +15420,11 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>1</v>
@@ -14251,11 +15451,11 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1</v>
@@ -14277,12 +15477,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -14308,16 +15508,16 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>赵世文</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0.6111111111111112</v>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>1</v>
@@ -14344,7 +15544,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -14375,17 +15575,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="24">
@@ -14406,11 +15606,11 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>张浩</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>1</v>
+          <t>谷晨旭</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>1</v>
@@ -14437,17 +15637,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="6" t="n">
-        <v>1</v>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -14468,7 +15668,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -14489,27 +15689,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>王佳琦</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0.3333333333333333</v>
+          <t>严绍源</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -14520,21 +15720,21 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>0</v>
+          <t>申谭谭</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>1</v>
@@ -14551,27 +15751,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="30">
@@ -14582,21 +15782,21 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>1</v>
@@ -14618,12 +15818,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
@@ -14649,12 +15849,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
@@ -14685,7 +15885,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
@@ -14695,7 +15895,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -14716,14 +15916,14 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>张亦浩</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>1</v>
+          <t>黄诺</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.6111111111111112</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0</v>
@@ -14737,21 +15937,21 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>1</v>
@@ -14768,21 +15968,21 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>1</v>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>1</v>
@@ -14799,21 +15999,21 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>杨博岚</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>1</v>
+          <t>刘佳欣</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>1</v>
@@ -14830,27 +16030,27 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="6" t="n">
-        <v>1</v>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -14861,27 +16061,27 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0</v>
+      <c r="F39" s="5" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -14902,17 +16102,17 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="41">
@@ -14933,17 +16133,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>1</v>
+          <t>张宝华</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.6111111111111112</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="G41" s="3" t="e">
-        <v>#N/A</v>
+      <c r="G41" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -14964,11 +16164,11 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>1</v>
@@ -14995,17 +16195,17 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="44">
@@ -15026,14 +16226,14 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>王旭炀</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0</v>
+          <t>曹添傲</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>0</v>
@@ -15057,17 +16257,265 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>王星晨</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>1</v>
+          <t>李梦瑶</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>李洋</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>翟林志</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>闫慧清</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>闫欣雨</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>马浩楠</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.3888888888888889</v>
       </c>
     </row>
   </sheetData>
